--- a/fhir/StructureDefinition-ehealth-referenceRange.xlsx
+++ b/fhir/StructureDefinition-ehealth-referenceRange.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-referenceRange.xlsx
+++ b/fhir/StructureDefinition-ehealth-referenceRange.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-referenceRange.xlsx
+++ b/fhir/StructureDefinition-ehealth-referenceRange.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-referenceRange.xlsx
+++ b/fhir/StructureDefinition-ehealth-referenceRange.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="139">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -387,54 +387,58 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
+  </si>
+  <si>
+    <t>Extension.extension:high</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>Extension.extension:high.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:high.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:high.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:high.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Extension.extension:type.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:type.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://ehealth.sundhed.dk/vs/reference-range-type</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
-  </si>
-  <si>
-    <t>Extension.extension:high</t>
-  </si>
-  <si>
-    <t>high</t>
-  </si>
-  <si>
-    <t>Extension.extension:high.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:high.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:high.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:high.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:type</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://ehealth.sundhed.dk/vs/reference-range-type</t>
   </si>
   <si>
     <t>base64Binary
@@ -2762,7 +2766,7 @@
         <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>114</v>
@@ -2901,7 +2905,7 @@
         <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>118</v>
@@ -2970,7 +2974,7 @@
         <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>114</v>

--- a/fhir/StructureDefinition-ehealth-referenceRange.xlsx
+++ b/fhir/StructureDefinition-ehealth-referenceRange.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-referenceRange.xlsx
+++ b/fhir/StructureDefinition-ehealth-referenceRange.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-referenceRange.xlsx
+++ b/fhir/StructureDefinition-ehealth-referenceRange.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
